--- a/ARQVJ2026-main/Assets/StreamingAssets/Blueprints/Blueprints.xlsx
+++ b/ARQVJ2026-main/Assets/StreamingAssets/Blueprints/Blueprints.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="Animals" sheetId="1" r:id="rId5"/>
+    <sheet state="visible" name="Tile Types" sheetId="1" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -11,48 +11,54 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="16">
   <si>
     <t>IDS</t>
   </si>
   <si>
-    <t>Life</t>
+    <t>Is Structure</t>
   </si>
   <si>
-    <t>Food</t>
+    <t>Is Walkable</t>
   </si>
   <si>
-    <t>Name</t>
+    <t>Is Animal Habitat</t>
   </si>
   <si>
-    <t>Monkey</t>
+    <t>Can Spawn Humans</t>
   </si>
   <si>
-    <t>100,200</t>
+    <t>Can Dispawn Humans</t>
   </si>
   <si>
-    <t>20</t>
+    <t>Is Default</t>
   </si>
   <si>
-    <t>Pepe</t>
+    <t>Road</t>
   </si>
   <si>
-    <t>Snake</t>
+    <t>FALSE</t>
   </si>
   <si>
-    <t>3</t>
+    <t>TRUE</t>
   </si>
   <si>
-    <t>Jose</t>
+    <t>Jail walls</t>
   </si>
   <si>
-    <t>RecontraBird</t>
+    <t>Jail habitat</t>
   </si>
   <si>
-    <t>14</t>
+    <t>Power Suply</t>
   </si>
   <si>
-    <t>Piolin!</t>
+    <t>Humans entry</t>
+  </si>
+  <si>
+    <t>Humans exit</t>
+  </si>
+  <si>
+    <t>Grass</t>
   </si>
 </sst>
 </file>
@@ -310,6 +316,13 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="12.38"/>
+    <col customWidth="1" min="2" max="3" width="9.5"/>
+    <col customWidth="1" min="4" max="4" width="13.63"/>
+    <col customWidth="1" min="5" max="5" width="16.25"/>
+    <col customWidth="1" min="6" max="6" width="17.63"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
@@ -324,9 +337,15 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
@@ -349,20 +368,26 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
+      <c r="E2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>8</v>
+      </c>
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
       <c r="J2" s="2"/>
@@ -385,20 +410,26 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>5</v>
+      <c r="D3" s="1" t="s">
+        <v>8</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>9</v>
+      <c r="E3" s="1" t="s">
+        <v>8</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>10</v>
+      <c r="F3" s="1" t="s">
+        <v>8</v>
       </c>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
+      <c r="G3" s="1" t="s">
+        <v>8</v>
+      </c>
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>
       <c r="J3" s="2"/>
@@ -424,17 +455,23 @@
         <v>11</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
+      <c r="E4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>8</v>
+      </c>
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
       <c r="J4" s="2"/>
@@ -457,20 +494,26 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
+      <c r="E5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>8</v>
+      </c>
       <c r="H5" s="2"/>
       <c r="I5" s="2"/>
       <c r="J5" s="2"/>
@@ -492,13 +535,27 @@
       <c r="Z5" s="2"/>
     </row>
     <row r="6">
-      <c r="A6" s="2"/>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
+      <c r="A6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>8</v>
+      </c>
       <c r="H6" s="2"/>
       <c r="I6" s="2"/>
       <c r="J6" s="2"/>
@@ -520,13 +577,27 @@
       <c r="Z6" s="2"/>
     </row>
     <row r="7">
-      <c r="A7" s="2"/>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
+      <c r="A7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>8</v>
+      </c>
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
       <c r="J7" s="2"/>
@@ -548,13 +619,27 @@
       <c r="Z7" s="2"/>
     </row>
     <row r="8">
-      <c r="A8" s="2"/>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
+      <c r="A8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>9</v>
+      </c>
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
       <c r="J8" s="2"/>

--- a/ARQVJ2026-main/Assets/StreamingAssets/Blueprints/Blueprints.xlsx
+++ b/ARQVJ2026-main/Assets/StreamingAssets/Blueprints/Blueprints.xlsx
@@ -4,6 +4,7 @@
   <workbookPr/>
   <sheets>
     <sheet state="visible" name="Tile Types" sheetId="1" r:id="rId5"/>
+    <sheet state="visible" name="Day Night Cycle" sheetId="2" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -11,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="24">
   <si>
     <t>IDS</t>
   </si>
@@ -60,6 +61,30 @@
   <si>
     <t>Grass</t>
   </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Duration</t>
+  </si>
+  <si>
+    <t>Morning</t>
+  </si>
+  <si>
+    <t>MidDay</t>
+  </si>
+  <si>
+    <t>Afternoon</t>
+  </si>
+  <si>
+    <t>Evening</t>
+  </si>
+  <si>
+    <t>Sunrise</t>
+  </si>
+  <si>
+    <t>Dusk</t>
+  </si>
 </sst>
 </file>
 
@@ -92,7 +117,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -100,6 +125,9 @@
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="49" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -109,6 +137,10 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
@@ -28439,4 +28471,93 @@
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" s="3">
+        <v>60.0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" s="3">
+        <v>60.0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" s="3">
+        <v>60.0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" s="3">
+        <v>60.0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" s="3">
+        <v>60.0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" s="3">
+        <v>60.0</v>
+      </c>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>
--- a/ARQVJ2026-main/Assets/StreamingAssets/Blueprints/Blueprints.xlsx
+++ b/ARQVJ2026-main/Assets/StreamingAssets/Blueprints/Blueprints.xlsx
@@ -5,6 +5,8 @@
   <sheets>
     <sheet state="visible" name="Tile Types" sheetId="1" r:id="rId5"/>
     <sheet state="visible" name="Day Night Cycle" sheetId="2" r:id="rId6"/>
+    <sheet state="visible" name="Animals" sheetId="3" r:id="rId7"/>
+    <sheet state="visible" name="Prefabs View" sheetId="4" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -12,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="29">
   <si>
     <t>IDS</t>
   </si>
@@ -85,6 +87,21 @@
   <si>
     <t>Dusk</t>
   </si>
+  <si>
+    <t>Monkey</t>
+  </si>
+  <si>
+    <t>Architecture ID</t>
+  </si>
+  <si>
+    <t>Prefab resource path</t>
+  </si>
+  <si>
+    <t>Monkey view</t>
+  </si>
+  <si>
+    <t>Prefabs/Entities/LivingEntities/Animals/Monkey.prefab</t>
+  </si>
 </sst>
 </file>
 
@@ -141,6 +158,14 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
@@ -28560,4 +28585,70 @@
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <cols>
+    <col customWidth="1" min="2" max="2" width="17.0"/>
+    <col customWidth="1" min="3" max="3" width="42.13"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>
--- a/ARQVJ2026-main/Assets/StreamingAssets/Blueprints/Blueprints.xlsx
+++ b/ARQVJ2026-main/Assets/StreamingAssets/Blueprints/Blueprints.xlsx
@@ -100,7 +100,7 @@
     <t>Monkey view</t>
   </si>
   <si>
-    <t>Prefabs/Entities/LivingEntities/Animals/Monkey.prefab</t>
+    <t>Prefabs/Entities/LivingEntities/Animals/Monkey</t>
   </si>
 </sst>
 </file>

--- a/ARQVJ2026-main/Assets/StreamingAssets/Blueprints/Blueprints.xlsx
+++ b/ARQVJ2026-main/Assets/StreamingAssets/Blueprints/Blueprints.xlsx
@@ -4,9 +4,10 @@
   <workbookPr/>
   <sheets>
     <sheet state="visible" name="Tile Types" sheetId="1" r:id="rId5"/>
-    <sheet state="visible" name="Day Night Cycle" sheetId="2" r:id="rId6"/>
-    <sheet state="visible" name="Animals" sheetId="3" r:id="rId7"/>
-    <sheet state="visible" name="Prefabs View" sheetId="4" r:id="rId8"/>
+    <sheet state="visible" name="Tiles View" sheetId="2" r:id="rId6"/>
+    <sheet state="visible" name="Day Night Cycle" sheetId="3" r:id="rId7"/>
+    <sheet state="visible" name="Animals" sheetId="4" r:id="rId8"/>
+    <sheet state="visible" name="Prefabs View" sheetId="5" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -14,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="50">
   <si>
     <t>IDS</t>
   </si>
@@ -64,6 +65,48 @@
     <t>Grass</t>
   </si>
   <si>
+    <t>Architecture ID</t>
+  </si>
+  <si>
+    <t>Prefab resource path</t>
+  </si>
+  <si>
+    <t>Road View</t>
+  </si>
+  <si>
+    <t>Prefabs/Map/YellowTile</t>
+  </si>
+  <si>
+    <t>Jail walls View</t>
+  </si>
+  <si>
+    <t>Prefabs/Map/RedTile</t>
+  </si>
+  <si>
+    <t>Jail habitat View</t>
+  </si>
+  <si>
+    <t>Prefabs/Map/LightblueTile</t>
+  </si>
+  <si>
+    <t>Power Suply View</t>
+  </si>
+  <si>
+    <t>Prefabs/Map/WhiteTile</t>
+  </si>
+  <si>
+    <t>Humans entry View</t>
+  </si>
+  <si>
+    <t>Humans exit View</t>
+  </si>
+  <si>
+    <t>Grass View</t>
+  </si>
+  <si>
+    <t>Prefabs/Map/GreenTile</t>
+  </si>
+  <si>
     <t>Name</t>
   </si>
   <si>
@@ -91,16 +134,37 @@
     <t>Monkey</t>
   </si>
   <si>
-    <t>Architecture ID</t>
+    <t>Bird</t>
   </si>
   <si>
-    <t>Prefab resource path</t>
+    <t>Snake</t>
+  </si>
+  <si>
+    <t>Lion</t>
   </si>
   <si>
     <t>Monkey view</t>
   </si>
   <si>
     <t>Prefabs/Entities/LivingEntities/Animals/Monkey</t>
+  </si>
+  <si>
+    <t>Bird view</t>
+  </si>
+  <si>
+    <t>Prefabs/Entities/LivingEntities/Animals/Bird</t>
+  </si>
+  <si>
+    <t>Snake view</t>
+  </si>
+  <si>
+    <t>Prefabs/Entities/LivingEntities/Animals/Snake</t>
+  </si>
+  <si>
+    <t>Lion view</t>
+  </si>
+  <si>
+    <t>Prefabs/Entities/LivingEntities/Animals/Lion</t>
   </si>
 </sst>
 </file>
@@ -166,6 +230,10 @@
 </file>
 
 <file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
@@ -28504,6 +28572,10 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="15.13"/>
+    <col customWidth="1" min="3" max="3" width="35.63"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="3" t="s">
@@ -28517,69 +28589,80 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>18</v>
+      <c r="B2" s="1" t="s">
+        <v>7</v>
       </c>
-      <c r="C2" s="3">
-        <v>60.0</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="s">
+      <c r="C2" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C3" s="3">
-        <v>60.0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="s">
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>20</v>
+      <c r="B3" s="1" t="s">
+        <v>10</v>
       </c>
-      <c r="C4" s="3">
-        <v>60.0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="s">
+      <c r="C3" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C5" s="3">
-        <v>60.0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="s">
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>22</v>
+      <c r="B4" s="1" t="s">
+        <v>11</v>
       </c>
-      <c r="C6" s="3">
-        <v>60.0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="s">
+      <c r="C4" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>23</v>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="s">
+        <v>24</v>
       </c>
-      <c r="C7" s="3">
-        <v>60.0</v>
+      <c r="B5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -28599,15 +28682,76 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>16</v>
+        <v>30</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>24</v>
+        <v>32</v>
+      </c>
+      <c r="C2" s="3">
+        <v>60.0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3" s="3">
+        <v>60.0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C4" s="3">
+        <v>60.0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C5" s="3">
+        <v>60.0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C6" s="3">
+        <v>60.0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C7" s="3">
+        <v>60.0</v>
       </c>
     </row>
   </sheetData>
@@ -28616,6 +28760,58 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -28631,21 +28827,54 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>28</v>
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>49</v>
       </c>
     </row>
   </sheetData>

--- a/ARQVJ2026-main/Assets/StreamingAssets/Blueprints/Blueprints.xlsx
+++ b/ARQVJ2026-main/Assets/StreamingAssets/Blueprints/Blueprints.xlsx
@@ -5,9 +5,10 @@
   <sheets>
     <sheet state="visible" name="Tile Types" sheetId="1" r:id="rId5"/>
     <sheet state="visible" name="Tiles View" sheetId="2" r:id="rId6"/>
-    <sheet state="visible" name="Day Night Cycle" sheetId="3" r:id="rId7"/>
-    <sheet state="visible" name="Animals" sheetId="4" r:id="rId8"/>
-    <sheet state="visible" name="Prefabs View" sheetId="5" r:id="rId9"/>
+    <sheet state="visible" name="UI View" sheetId="3" r:id="rId7"/>
+    <sheet state="visible" name="Prefabs View" sheetId="4" r:id="rId8"/>
+    <sheet state="visible" name="Day Night Cycle" sheetId="5" r:id="rId9"/>
+    <sheet state="visible" name="Animals" sheetId="6" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -15,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="56">
   <si>
     <t>IDS</t>
   </si>
@@ -107,6 +108,60 @@
     <t>Prefabs/Map/GreenTile</t>
   </si>
   <si>
+    <t>MENU_CONTAINER</t>
+  </si>
+  <si>
+    <t>ContextMenuContainer</t>
+  </si>
+  <si>
+    <t>Prefabs/UI/ContextMenuContainer</t>
+  </si>
+  <si>
+    <t>BUTTON</t>
+  </si>
+  <si>
+    <t>ButtonPrefab</t>
+  </si>
+  <si>
+    <t>Prefabs/UI/ButtonPrefab</t>
+  </si>
+  <si>
+    <t>Monkey view</t>
+  </si>
+  <si>
+    <t>Monkey</t>
+  </si>
+  <si>
+    <t>Prefabs/Entities/LivingEntities/Animals/Monkey</t>
+  </si>
+  <si>
+    <t>Bird view</t>
+  </si>
+  <si>
+    <t>Bird</t>
+  </si>
+  <si>
+    <t>Prefabs/Entities/LivingEntities/Animals/Bird</t>
+  </si>
+  <si>
+    <t>Snake view</t>
+  </si>
+  <si>
+    <t>Snake</t>
+  </si>
+  <si>
+    <t>Prefabs/Entities/LivingEntities/Animals/Snake</t>
+  </si>
+  <si>
+    <t>Lion view</t>
+  </si>
+  <si>
+    <t>Lion</t>
+  </si>
+  <si>
+    <t>Prefabs/Entities/LivingEntities/Animals/Lion</t>
+  </si>
+  <si>
     <t>Name</t>
   </si>
   <si>
@@ -129,42 +184,6 @@
   </si>
   <si>
     <t>Dusk</t>
-  </si>
-  <si>
-    <t>Monkey</t>
-  </si>
-  <si>
-    <t>Bird</t>
-  </si>
-  <si>
-    <t>Snake</t>
-  </si>
-  <si>
-    <t>Lion</t>
-  </si>
-  <si>
-    <t>Monkey view</t>
-  </si>
-  <si>
-    <t>Prefabs/Entities/LivingEntities/Animals/Monkey</t>
-  </si>
-  <si>
-    <t>Bird view</t>
-  </si>
-  <si>
-    <t>Prefabs/Entities/LivingEntities/Animals/Bird</t>
-  </si>
-  <si>
-    <t>Snake view</t>
-  </si>
-  <si>
-    <t>Prefabs/Entities/LivingEntities/Animals/Snake</t>
-  </si>
-  <si>
-    <t>Lion view</t>
-  </si>
-  <si>
-    <t>Prefabs/Entities/LivingEntities/Animals/Lion</t>
   </si>
 </sst>
 </file>
@@ -234,6 +253,10 @@
 </file>
 
 <file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
@@ -28676,27 +28699,32 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="16.5"/>
+    <col customWidth="1" min="2" max="2" width="18.13"/>
+    <col customWidth="1" min="3" max="3" width="26.5"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="B2" s="3" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="3" t="s">
+      <c r="C2" s="3" t="s">
         <v>32</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C2" s="3">
-        <v>60.0</v>
       </c>
     </row>
     <row r="3">
@@ -28704,54 +28732,10 @@
         <v>33</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C3" s="3">
-        <v>60.0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C4" s="3">
-        <v>60.0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="s">
+      <c r="C3" s="3" t="s">
         <v>35</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="C5" s="3">
-        <v>60.0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="C6" s="3">
-        <v>60.0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="C7" s="3">
-        <v>60.0</v>
       </c>
     </row>
   </sheetData>
@@ -28760,58 +28744,6 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>41</v>
-      </c>
-    </row>
-  </sheetData>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -28835,46 +28767,187 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="C2" s="3" t="s">
+      <c r="B4" s="3" t="s">
         <v>43</v>
       </c>
+      <c r="C4" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C2" s="3">
+        <v>60.0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>45</v>
+      <c r="C3" s="3">
+        <v>60.0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C4" s="3">
+        <v>60.0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C5" s="3">
+        <v>60.0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C6" s="3">
+        <v>60.0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C7" s="3">
+        <v>60.0</v>
+      </c>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="s">
-        <v>48</v>
-      </c>
       <c r="B5" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>

--- a/ARQVJ2026-main/Assets/StreamingAssets/Blueprints/Blueprints.xlsx
+++ b/ARQVJ2026-main/Assets/StreamingAssets/Blueprints/Blueprints.xlsx
@@ -6,9 +6,10 @@
     <sheet state="visible" name="Tile Types" sheetId="1" r:id="rId5"/>
     <sheet state="visible" name="Tiles View" sheetId="2" r:id="rId6"/>
     <sheet state="visible" name="UI View" sheetId="3" r:id="rId7"/>
-    <sheet state="visible" name="Prefabs View" sheetId="4" r:id="rId8"/>
-    <sheet state="visible" name="Day Night Cycle" sheetId="5" r:id="rId9"/>
-    <sheet state="visible" name="Animals" sheetId="6" r:id="rId10"/>
+    <sheet state="visible" name="Cameras View" sheetId="4" r:id="rId8"/>
+    <sheet state="visible" name="Prefabs View" sheetId="5" r:id="rId9"/>
+    <sheet state="visible" name="Day Night Cycle" sheetId="6" r:id="rId10"/>
+    <sheet state="visible" name="Animals" sheetId="7" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -16,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="59">
   <si>
     <t>IDS</t>
   </si>
@@ -124,6 +125,15 @@
   </si>
   <si>
     <t>Prefabs/UI/ButtonPrefab</t>
+  </si>
+  <si>
+    <t>GAME_CAMERA</t>
+  </si>
+  <si>
+    <t>GameCamera</t>
+  </si>
+  <si>
+    <t>Prefabs/Camera/GameCamera</t>
   </si>
   <si>
     <t>Monkey view</t>
@@ -257,6 +267,10 @@
 </file>
 
 <file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
@@ -28750,6 +28764,45 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
+    <col customWidth="1" min="1" max="1" width="14.0"/>
+    <col customWidth="1" min="2" max="2" width="18.13"/>
+    <col customWidth="1" min="3" max="3" width="26.5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <cols>
     <col customWidth="1" min="2" max="2" width="17.0"/>
     <col customWidth="1" min="3" max="3" width="42.13"/>
   </cols>
@@ -28767,135 +28820,46 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>47</v>
-      </c>
-    </row>
-  </sheetData>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="3" t="s">
         <v>50</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="C2" s="3">
-        <v>60.0</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C3" s="3">
-        <v>60.0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="C4" s="3">
-        <v>60.0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="C5" s="3">
-        <v>60.0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="C6" s="3">
-        <v>60.0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="C7" s="3">
-        <v>60.0</v>
       </c>
     </row>
   </sheetData>
@@ -28915,39 +28879,128 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>48</v>
+        <v>51</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>37</v>
+        <v>53</v>
+      </c>
+      <c r="C2" s="3">
+        <v>60.0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C3" s="3">
+        <v>60.0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C4" s="3">
+        <v>60.0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C5" s="3">
+        <v>60.0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C6" s="3">
+        <v>60.0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C7" s="3">
+        <v>60.0</v>
+      </c>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B2" s="3" t="s">
         <v>40</v>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>

--- a/ARQVJ2026-main/Assets/StreamingAssets/Blueprints/Blueprints.xlsx
+++ b/ARQVJ2026-main/Assets/StreamingAssets/Blueprints/Blueprints.xlsx
@@ -7,7 +7,7 @@
     <sheet state="visible" name="Tiles View" sheetId="2" r:id="rId6"/>
     <sheet state="visible" name="UI View" sheetId="3" r:id="rId7"/>
     <sheet state="visible" name="Cameras View" sheetId="4" r:id="rId8"/>
-    <sheet state="visible" name="Prefabs View" sheetId="5" r:id="rId9"/>
+    <sheet state="visible" name="Animals View" sheetId="5" r:id="rId9"/>
     <sheet state="visible" name="Day Night Cycle" sheetId="6" r:id="rId10"/>
     <sheet state="visible" name="Animals" sheetId="7" r:id="rId11"/>
   </sheets>
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="60">
   <si>
     <t>IDS</t>
   </si>
@@ -194,6 +194,9 @@
   </si>
   <si>
     <t>Dusk</t>
+  </si>
+  <si>
+    <t>Food needed per day</t>
   </si>
 </sst>
 </file>
@@ -28962,6 +28965,9 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <cols>
+    <col customWidth="1" min="3" max="3" width="16.88"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="3" t="s">
@@ -28970,6 +28976,9 @@
       <c r="B1" s="3" t="s">
         <v>51</v>
       </c>
+      <c r="C1" s="3" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
@@ -28978,6 +28987,9 @@
       <c r="B2" s="3" t="s">
         <v>40</v>
       </c>
+      <c r="C2" s="3">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
@@ -28986,6 +28998,9 @@
       <c r="B3" s="3" t="s">
         <v>43</v>
       </c>
+      <c r="C3" s="3">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
@@ -28994,6 +29009,9 @@
       <c r="B4" s="3" t="s">
         <v>46</v>
       </c>
+      <c r="C4" s="3">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
@@ -29002,6 +29020,9 @@
       <c r="B5" s="3" t="s">
         <v>49</v>
       </c>
+      <c r="C5" s="3">
+        <v>1.0</v>
+      </c>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>

--- a/ARQVJ2026-main/Assets/StreamingAssets/Blueprints/Blueprints.xlsx
+++ b/ARQVJ2026-main/Assets/StreamingAssets/Blueprints/Blueprints.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="61">
   <si>
     <t>IDS</t>
   </si>
@@ -38,6 +38,9 @@
   </si>
   <si>
     <t>Is Default</t>
+  </si>
+  <si>
+    <t>Is Unique</t>
   </si>
   <si>
     <t>Road</t>
@@ -511,7 +514,9 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2"/>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
       <c r="K1" s="2"/>
@@ -533,27 +538,29 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>8</v>
-      </c>
       <c r="E2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
-      <c r="H2" s="2"/>
+      <c r="H2" s="1" t="s">
+        <v>9</v>
+      </c>
       <c r="I2" s="2"/>
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
@@ -575,27 +582,29 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="C3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>8</v>
-      </c>
       <c r="D3" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
-      <c r="H3" s="2"/>
+      <c r="H3" s="1" t="s">
+        <v>9</v>
+      </c>
       <c r="I3" s="2"/>
       <c r="J3" s="2"/>
       <c r="K3" s="2"/>
@@ -617,27 +626,29 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E4" s="1" t="s">
-        <v>8</v>
-      </c>
       <c r="F4" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
-      <c r="H4" s="2"/>
+      <c r="H4" s="1" t="s">
+        <v>9</v>
+      </c>
       <c r="I4" s="2"/>
       <c r="J4" s="2"/>
       <c r="K4" s="2"/>
@@ -659,27 +670,29 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>8</v>
-      </c>
       <c r="D5" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
-      <c r="H5" s="2"/>
+      <c r="H5" s="1" t="s">
+        <v>9</v>
+      </c>
       <c r="I5" s="2"/>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
@@ -701,27 +714,29 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D6" s="1" t="s">
-        <v>8</v>
+      <c r="E6" s="1" t="s">
+        <v>10</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="F6" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F6" s="1" t="s">
-        <v>8</v>
+      <c r="G6" s="1" t="s">
+        <v>9</v>
       </c>
-      <c r="G6" s="1" t="s">
-        <v>8</v>
+      <c r="H6" s="1" t="s">
+        <v>10</v>
       </c>
-      <c r="H6" s="2"/>
       <c r="I6" s="2"/>
       <c r="J6" s="2"/>
       <c r="K6" s="2"/>
@@ -743,27 +758,29 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D7" s="1" t="s">
-        <v>8</v>
-      </c>
       <c r="E7" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G7" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G7" s="1" t="s">
-        <v>8</v>
+      <c r="H7" s="1" t="s">
+        <v>10</v>
       </c>
-      <c r="H7" s="2"/>
       <c r="I7" s="2"/>
       <c r="J7" s="2"/>
       <c r="K7" s="2"/>
@@ -785,27 +802,29 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C8" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="1" t="s">
-        <v>8</v>
-      </c>
       <c r="E8" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G8" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H8" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="H8" s="2"/>
       <c r="I8" s="2"/>
       <c r="J8" s="2"/>
       <c r="K8" s="2"/>
@@ -28622,87 +28641,87 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>15</v>
-      </c>
       <c r="C8" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -28727,32 +28746,32 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -28777,21 +28796,21 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -28815,54 +28834,54 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>
@@ -28882,18 +28901,18 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C2" s="3">
         <v>60.0</v>
@@ -28901,10 +28920,10 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C3" s="3">
         <v>60.0</v>
@@ -28912,10 +28931,10 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C4" s="3">
         <v>60.0</v>
@@ -28923,10 +28942,10 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C5" s="3">
         <v>60.0</v>
@@ -28934,10 +28953,10 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C6" s="3">
         <v>60.0</v>
@@ -28945,10 +28964,10 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C7" s="3">
         <v>60.0</v>
@@ -28974,18 +28993,18 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C2" s="3">
         <v>1.0</v>
@@ -28993,10 +29012,10 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C3" s="3">
         <v>1.0</v>
@@ -29004,10 +29023,10 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C4" s="3">
         <v>1.0</v>
@@ -29015,10 +29034,10 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C5" s="3">
         <v>1.0</v>

--- a/ARQVJ2026-main/Assets/StreamingAssets/Blueprints/Blueprints.xlsx
+++ b/ARQVJ2026-main/Assets/StreamingAssets/Blueprints/Blueprints.xlsx
@@ -4,17 +4,18 @@
   <workbookPr/>
   <sheets>
     <sheet state="visible" name="Resources" sheetId="1" r:id="rId5"/>
-    <sheet state="visible" name="UI View" sheetId="2" r:id="rId6"/>
-    <sheet state="visible" name="Cameras View" sheetId="3" r:id="rId7"/>
-    <sheet state="visible" name="Day Night Cycle" sheetId="4" r:id="rId8"/>
-    <sheet state="visible" name="Tile Types" sheetId="5" r:id="rId9"/>
-    <sheet state="visible" name="Tiles View" sheetId="6" r:id="rId10"/>
-    <sheet state="visible" name="Animals" sheetId="7" r:id="rId11"/>
-    <sheet state="visible" name="Animals View" sheetId="8" r:id="rId12"/>
-    <sheet state="visible" name="Jails" sheetId="9" r:id="rId13"/>
-    <sheet state="visible" name="Jails View" sheetId="10" r:id="rId14"/>
-    <sheet state="visible" name="Infrastructure" sheetId="11" r:id="rId15"/>
-    <sheet state="visible" name="Infrastructure View" sheetId="12" r:id="rId16"/>
+    <sheet state="visible" name="Rules" sheetId="2" r:id="rId6"/>
+    <sheet state="visible" name="UI View" sheetId="3" r:id="rId7"/>
+    <sheet state="visible" name="Cameras View" sheetId="4" r:id="rId8"/>
+    <sheet state="visible" name="Day Night Cycle" sheetId="5" r:id="rId9"/>
+    <sheet state="visible" name="Tile Types" sheetId="6" r:id="rId10"/>
+    <sheet state="visible" name="Tiles View" sheetId="7" r:id="rId11"/>
+    <sheet state="visible" name="Animals" sheetId="8" r:id="rId12"/>
+    <sheet state="visible" name="Animals View" sheetId="9" r:id="rId13"/>
+    <sheet state="visible" name="Jails" sheetId="10" r:id="rId14"/>
+    <sheet state="visible" name="Jails View" sheetId="11" r:id="rId15"/>
+    <sheet state="visible" name="Infrastructure" sheetId="12" r:id="rId16"/>
+    <sheet state="visible" name="Infrastructure View" sheetId="13" r:id="rId17"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -22,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="138">
   <si>
     <t>IDS</t>
   </si>
@@ -36,7 +37,7 @@
     <t>Max posible value</t>
   </si>
   <si>
-    <t>Start amount</t>
+    <t>Current value</t>
   </si>
   <si>
     <t>Money</t>
@@ -45,7 +46,7 @@
     <t>9223372036854775807</t>
   </si>
   <si>
-    <t>AminalFood</t>
+    <t>AnimalFood</t>
   </si>
   <si>
     <t>Aminal food</t>
@@ -67,6 +68,39 @@
   </si>
   <si>
     <t>Animals</t>
+  </si>
+  <si>
+    <t>Ids</t>
+  </si>
+  <si>
+    <t>Value A</t>
+  </si>
+  <si>
+    <t>Value B</t>
+  </si>
+  <si>
+    <t>Operator</t>
+  </si>
+  <si>
+    <t>CanBuyAnimal</t>
+  </si>
+  <si>
+    <t>Animals - Monkey - Price</t>
+  </si>
+  <si>
+    <t>Resources - Money - Current value</t>
+  </si>
+  <si>
+    <t>&gt;=</t>
+  </si>
+  <si>
+    <t>CanAnimalBeFeeded</t>
+  </si>
+  <si>
+    <t>Animals - Monkey - Food needed per day</t>
+  </si>
+  <si>
+    <t>Resources - AnimalFood - Current value</t>
   </si>
   <si>
     <t>Architecture ID</t>
@@ -208,6 +242,9 @@
   </si>
   <si>
     <t>Prefabs/Map/GreenTile</t>
+  </si>
+  <si>
+    <t>Can be feeded rule</t>
   </si>
   <si>
     <t>Food needed per day</t>
@@ -478,6 +515,10 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
+<file path=xl/drawings/drawing13.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
@@ -867,7 +908,7 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
-    <col customWidth="1" min="3" max="3" width="35.63"/>
+    <col customWidth="1" min="2" max="3" width="22.63"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -875,21 +916,15 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>16</v>
+        <v>127</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>118</v>
+        <v>128</v>
+      </c>
+      <c r="B2" s="1">
+        <v>1.0</v>
       </c>
     </row>
   </sheetData>
@@ -904,51 +939,30 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
-    <col customWidth="1" min="3" max="3" width="22.63"/>
+    <col customWidth="1" min="3" max="3" width="35.63"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>115</v>
+      <c r="B1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="C2" s="5">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="C3" s="5">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="4"/>
-      <c r="B4" s="4"/>
-      <c r="C4" s="5"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="4"/>
-      <c r="B5" s="4"/>
-      <c r="C5" s="5"/>
+      <c r="A2" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>130</v>
+      </c>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
@@ -962,6 +976,64 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
+    <col customWidth="1" min="3" max="3" width="22.63"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="C2" s="5">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="C3" s="5">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4"/>
+      <c r="B4" s="4"/>
+      <c r="C4" s="5"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="4"/>
+      <c r="B5" s="4"/>
+      <c r="C5" s="5"/>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <cols>
     <col customWidth="1" min="3" max="3" width="39.5"/>
   </cols>
   <sheetData>
@@ -970,32 +1042,32 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="4" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>123</v>
+        <v>135</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="s">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
     </row>
   </sheetData>
@@ -1004,6 +1076,65 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="16.88"/>
+    <col customWidth="1" min="2" max="2" width="35.13"/>
+    <col customWidth="1" min="3" max="3" width="30.88"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -1020,32 +1151,32 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -1053,7 +1184,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -1070,21 +1201,21 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -1092,7 +1223,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -1107,15 +1238,15 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="C2" s="1">
         <v>60.0</v>
@@ -1123,10 +1254,10 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="C3" s="1">
         <v>60.0</v>
@@ -1134,10 +1265,10 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="C4" s="1">
         <v>60.0</v>
@@ -1145,10 +1276,10 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="C5" s="1">
         <v>60.0</v>
@@ -1156,10 +1287,10 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="C6" s="1">
         <v>60.0</v>
@@ -1167,10 +1298,10 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="C7" s="1">
         <v>60.0</v>
@@ -1181,7 +1312,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -1201,28 +1332,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="J1" s="3"/>
       <c r="K1" s="3"/>
@@ -1245,31 +1376,31 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="J2" s="3"/>
       <c r="K2" s="3"/>
@@ -1292,31 +1423,31 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="J3" s="3"/>
       <c r="K3" s="3"/>
@@ -1339,31 +1470,31 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="J4" s="3"/>
       <c r="K4" s="3"/>
@@ -1386,31 +1517,31 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="J5" s="3"/>
       <c r="K5" s="3"/>
@@ -1433,31 +1564,31 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="J6" s="3"/>
       <c r="K6" s="3"/>
@@ -1480,31 +1611,31 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="J7" s="3"/>
       <c r="K7" s="3"/>
@@ -1527,31 +1658,31 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="J8" s="3"/>
       <c r="K8" s="3"/>
@@ -30345,7 +30476,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -30361,87 +30492,87 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>47</v>
-      </c>
       <c r="C6" s="1" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>48</v>
-      </c>
       <c r="C7" s="1" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>49</v>
-      </c>
       <c r="C8" s="1" t="s">
-        <v>61</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -30449,15 +30580,15 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
-    <col customWidth="1" min="3" max="3" width="16.88"/>
-    <col customWidth="1" min="8" max="8" width="59.63"/>
+    <col customWidth="1" min="3" max="4" width="16.88"/>
+    <col customWidth="1" min="9" max="9" width="59.63"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -30468,334 +30599,373 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>67</v>
+        <v>78</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="C2" s="1">
+        <v>80</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2" s="1">
         <v>2.0</v>
       </c>
-      <c r="D2" s="1">
+      <c r="E2" s="1">
         <v>1.0</v>
       </c>
-      <c r="E2" s="1">
+      <c r="F2" s="1">
         <v>22.0</v>
       </c>
-      <c r="F2" s="1">
+      <c r="G2" s="1">
         <v>6.0</v>
       </c>
-      <c r="G2" s="1">
+      <c r="H2" s="1">
         <v>200.0</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>69</v>
+      <c r="I2" s="1" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="C3" s="1">
+        <v>82</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" s="1">
         <v>10.0</v>
       </c>
-      <c r="D3" s="1">
+      <c r="E3" s="1">
         <v>5.0</v>
       </c>
-      <c r="E3" s="1">
+      <c r="F3" s="1">
         <v>22.0</v>
       </c>
-      <c r="F3" s="1">
+      <c r="G3" s="1">
         <v>6.0</v>
       </c>
-      <c r="G3" s="1">
+      <c r="H3" s="1">
         <v>400.0</v>
       </c>
-      <c r="H3" s="1" t="s">
-        <v>71</v>
+      <c r="I3" s="1" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="C4" s="1">
+        <v>84</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" s="1">
         <v>5.0</v>
       </c>
-      <c r="D4" s="1">
+      <c r="E4" s="1">
         <v>2.0</v>
       </c>
-      <c r="E4" s="1">
+      <c r="F4" s="1">
         <v>22.0</v>
       </c>
-      <c r="F4" s="1">
+      <c r="G4" s="1">
         <v>6.0</v>
       </c>
-      <c r="G4" s="1">
+      <c r="H4" s="1">
         <v>200.0</v>
       </c>
-      <c r="H4" s="1" t="s">
-        <v>73</v>
+      <c r="I4" s="1" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="C5" s="1">
+        <v>86</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5" s="1">
         <v>5.0</v>
       </c>
-      <c r="D5" s="1">
+      <c r="E5" s="1">
         <v>2.0</v>
       </c>
-      <c r="E5" s="1">
+      <c r="F5" s="1">
         <v>22.0</v>
       </c>
-      <c r="F5" s="1">
+      <c r="G5" s="1">
         <v>6.0</v>
       </c>
-      <c r="G5" s="1">
+      <c r="H5" s="1">
         <v>300.0</v>
       </c>
-      <c r="H5" s="1" t="s">
-        <v>75</v>
+      <c r="I5" s="1" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="C6" s="1">
+        <v>88</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6" s="1">
         <v>20.0</v>
       </c>
-      <c r="D6" s="1">
+      <c r="E6" s="1">
         <v>3.0</v>
       </c>
-      <c r="E6" s="1">
+      <c r="F6" s="1">
         <v>22.0</v>
       </c>
-      <c r="F6" s="1">
+      <c r="G6" s="1">
         <v>6.0</v>
       </c>
-      <c r="G6" s="1">
+      <c r="H6" s="1">
         <v>500.0</v>
       </c>
-      <c r="H6" s="1" t="s">
-        <v>77</v>
+      <c r="I6" s="1" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="C7" s="1">
+        <v>90</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7" s="1">
         <v>10.0</v>
       </c>
-      <c r="D7" s="1">
+      <c r="E7" s="1">
         <v>5.0</v>
       </c>
-      <c r="E7" s="1">
+      <c r="F7" s="1">
         <v>22.0</v>
       </c>
-      <c r="F7" s="1">
+      <c r="G7" s="1">
         <v>6.0</v>
       </c>
-      <c r="G7" s="1">
+      <c r="H7" s="1">
         <v>400.0</v>
       </c>
-      <c r="H7" s="1" t="s">
-        <v>79</v>
+      <c r="I7" s="1" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="C8" s="1">
+        <v>92</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D8" s="1">
         <v>2.0</v>
       </c>
-      <c r="D8" s="1">
+      <c r="E8" s="1">
         <v>1.0</v>
       </c>
-      <c r="E8" s="1">
+      <c r="F8" s="1">
         <v>22.0</v>
       </c>
-      <c r="F8" s="1">
+      <c r="G8" s="1">
         <v>6.0</v>
       </c>
-      <c r="G8" s="1">
+      <c r="H8" s="1">
         <v>300.0</v>
       </c>
-      <c r="H8" s="1" t="s">
-        <v>81</v>
+      <c r="I8" s="1" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="C9" s="1">
-        <v>2.0</v>
+        <v>94</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="D9" s="1">
         <v>2.0</v>
       </c>
       <c r="E9" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="F9" s="1">
         <v>22.0</v>
       </c>
-      <c r="F9" s="1">
+      <c r="G9" s="1">
         <v>6.0</v>
       </c>
-      <c r="G9" s="1">
+      <c r="H9" s="1">
         <v>200.0</v>
       </c>
-      <c r="H9" s="1" t="s">
-        <v>70</v>
+      <c r="I9" s="1" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="C10" s="1">
+        <v>95</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D10" s="1">
         <v>15.0</v>
       </c>
-      <c r="D10" s="1">
+      <c r="E10" s="1">
         <v>2.0</v>
       </c>
-      <c r="E10" s="1">
+      <c r="F10" s="1">
         <v>22.0</v>
       </c>
-      <c r="F10" s="1">
+      <c r="G10" s="1">
         <v>6.0</v>
       </c>
-      <c r="G10" s="1">
+      <c r="H10" s="1">
         <v>700.0</v>
       </c>
-      <c r="H10" s="1" t="s">
-        <v>84</v>
+      <c r="I10" s="1" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="C11" s="1">
+        <v>97</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D11" s="1">
         <v>10.0</v>
       </c>
-      <c r="D11" s="1">
+      <c r="E11" s="1">
         <v>2.0</v>
       </c>
-      <c r="E11" s="1">
+      <c r="F11" s="1">
         <v>22.0</v>
       </c>
-      <c r="F11" s="1">
+      <c r="G11" s="1">
         <v>6.0</v>
       </c>
-      <c r="G11" s="1">
+      <c r="H11" s="1">
         <v>400.0</v>
       </c>
-      <c r="H11" s="1" t="s">
-        <v>86</v>
+      <c r="I11" s="1" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="C12" s="1">
+        <v>99</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D12" s="1">
         <v>15.0</v>
       </c>
-      <c r="D12" s="1">
+      <c r="E12" s="1">
         <v>4.0</v>
       </c>
-      <c r="E12" s="1">
+      <c r="F12" s="1">
         <v>22.0</v>
       </c>
-      <c r="F12" s="1">
+      <c r="G12" s="1">
         <v>6.0</v>
       </c>
-      <c r="G12" s="1">
+      <c r="H12" s="1">
         <v>600.0</v>
       </c>
-      <c r="H12" s="1" t="s">
-        <v>88</v>
+      <c r="I12" s="1" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="C13" s="1">
+        <v>101</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D13" s="1">
         <v>15.0</v>
       </c>
-      <c r="D13" s="1">
+      <c r="E13" s="1">
         <v>4.0</v>
       </c>
-      <c r="E13" s="1">
+      <c r="F13" s="1">
         <v>22.0</v>
       </c>
-      <c r="F13" s="1">
+      <c r="G13" s="1">
         <v>6.0</v>
       </c>
-      <c r="G13" s="1">
+      <c r="H13" s="1">
         <v>500.0</v>
       </c>
-      <c r="H13" s="1" t="s">
-        <v>90</v>
+      <c r="I13" s="1" t="s">
+        <v>102</v>
       </c>
     </row>
   </sheetData>
@@ -30803,7 +30973,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -30820,173 +30990,142 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>98</v>
+        <v>110</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>99</v>
+        <v>111</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>100</v>
+        <v>112</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>105</v>
+        <v>117</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>106</v>
+        <v>118</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>108</v>
+        <v>120</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
-        <v>111</v>
+        <v>123</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>114</v>
-      </c>
-    </row>
-  </sheetData>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
-  <cols>
-    <col customWidth="1" min="2" max="3" width="22.63"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="B2" s="1">
-        <v>1.0</v>
+        <v>126</v>
       </c>
     </row>
   </sheetData>
